--- a/Summary Key Behavior_Leadership Competency (IND & ENG).xlsx
+++ b/Summary Key Behavior_Leadership Competency (IND & ENG).xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satyamuk\OneDrive - PT Telekomunikasi Selular\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hdwic/Documents/Playground/MOANA/script-populate-lxp-comp-scoring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A43943D-9722-41CD-8E97-1036D275BE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50AFDEC-7364-1A4F-8492-AEF152CCB5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14480" yWindow="620" windowWidth="14320" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IND" sheetId="2" r:id="rId1"/>
     <sheet name="ENG" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IND!$A$2:$G$14</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="125">
   <si>
     <t>Kompetensi</t>
   </si>
@@ -446,7 +449,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,6 +483,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -597,11 +606,47 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -883,15 +928,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ABB97E3-A79A-0744-93E4-E3BBADD18E15}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="11" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="33.1640625" style="11" customWidth="1"/>
     <col min="3" max="7" width="40" style="12" customWidth="1"/>
-    <col min="8" max="16384" width="8.77734375" style="8"/>
+    <col min="8" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -906,7 +951,7 @@
       <c r="F1" s="14"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="1" t="s">
@@ -925,7 +970,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -948,7 +993,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="120" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -971,7 +1016,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -994,7 +1039,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -1017,7 +1062,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -1038,7 +1083,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -1059,7 +1104,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="138" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="135" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -1080,7 +1125,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="138" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="135" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -1097,45 +1142,35 @@
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
     </row>
-    <row r="11" spans="1:7" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="120" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>12</v>
-      </c>
+      <c r="C11" s="16"/>
       <c r="D11" s="7" t="s">
         <v>74</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>12</v>
-      </c>
+      <c r="F11" s="16"/>
       <c r="G11" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>12</v>
-      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
       <c r="F12" s="7" t="s">
         <v>114</v>
       </c>
@@ -1143,22 +1178,16 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="90" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>12</v>
-      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="5" t="s">
         <v>115</v>
       </c>
@@ -1166,22 +1195,16 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>12</v>
-      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
       <c r="F14" s="5" t="s">
         <v>117</v>
       </c>
@@ -1190,6 +1213,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:G14" xr:uid="{9ABB97E3-A79A-0744-93E4-E3BBADD18E15}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
@@ -1202,15 +1226,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C15D610-B6D1-45AB-AF84-E6050E36C196}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="11" customWidth="1"/>
-    <col min="2" max="2" width="34.77734375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="34.83203125" style="11" customWidth="1"/>
     <col min="3" max="7" width="40" style="12" customWidth="1"/>
-    <col min="8" max="16384" width="8.77734375" style="8"/>
+    <col min="8" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1225,7 +1249,7 @@
       <c r="F1" s="14"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="1" t="s">
@@ -1244,7 +1268,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1267,7 +1291,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1290,7 +1314,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -1313,7 +1337,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -1336,7 +1360,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -1357,7 +1381,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -1378,7 +1402,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -1399,7 +1423,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -1416,7 +1440,7 @@
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
     </row>
-    <row r="11" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
@@ -1439,7 +1463,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="105" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
@@ -1462,7 +1486,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="75" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>23</v>
       </c>
@@ -1485,7 +1509,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
